--- a/data/b2_centro/B2 Centro 08-2026.xlsx
+++ b/data/b2_centro/B2 Centro 08-2026.xlsx
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1482.87</v>
+        <v>1520.32</v>
       </c>
     </row>
     <row r="3">
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>79693.57000000001</v>
+        <v>77225.56</v>
       </c>
     </row>
     <row r="4">
@@ -4999,16 +4999,16 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1643.86</v>
+        <v>1695.45</v>
       </c>
     </row>
     <row r="5">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>5673.58</v>
+        <v>5275.19</v>
       </c>
     </row>
     <row r="6">
@@ -5071,21 +5071,21 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1749.03</v>
+        <v>1223.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -5094,29 +5094,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1433.28</v>
+        <v>2053.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>13940.04</v>
+        <v>1779.41</v>
       </c>
     </row>
     <row r="11">
@@ -5125,124 +5125,124 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>3630.11</v>
+        <v>12614.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>5735.2</v>
+        <v>4576.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2134.78</v>
+        <v>5976.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1672.13</v>
+        <v>27056.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>27150.04</v>
+        <v>1650.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3558.02</v>
+        <v>5472.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5942.63</v>
+        <v>3360.87</v>
       </c>
     </row>
     <row r="18">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5689.72</v>
+        <v>5953.15</v>
       </c>
     </row>
     <row r="19">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>828.46</v>
+        <v>795.39</v>
       </c>
     </row>
   </sheetData>
